--- a/artfynd/A 61824-2022 artfynd.xlsx
+++ b/artfynd/A 61824-2022 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>136183381</v>
       </c>
       <c r="B5" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
